--- a/gaming_forms/014_first_person_shooter_skills_quiz--gaming_forms.xlsx
+++ b/gaming_forms/014_first_person_shooter_skills_quiz--gaming_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>situational_awareness</t>
+          <t>situational_awareness_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Situational Awareness</t>
+          <t>Situational Awareness 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>decision_making</t>
+          <t>decision_making_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Decision Making</t>
+          <t>Decision Making 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>problem_solving</t>
+          <t>problem_solving_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Problem Solving</t>
+          <t>Problem Solving 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'cs':_'cs:go'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'CS': 'CS:GO'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'fps':_'fps'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'FPS': 'FPS'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'tps':_'tps'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'TPS': 'TPS'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1398,17 +1398,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>adaptability_choices</t>
+          <t>strategy_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>adaptable</t>
+          <t>tactician</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Adaptable</t>
+          <t>Tactician</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>tactician</t>
+          <t>aggressive</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tactician</t>
+          <t>Aggressive</t>
         </is>
       </c>
     </row>
@@ -1437,27 +1437,10 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>aggressive</t>
+          <t>defensive</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
-        <is>
-          <t>Aggressive</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>strategy_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>defensive</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
